--- a/presentaciones.xlsx
+++ b/presentaciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juanc\OneDrive\Documentos\LAB-MAA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39111D3F-919D-4C0A-BA56-01D1AAFE5813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAA29BE8-57E0-4D62-AD3F-03D443FC25D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -350,9 +350,6 @@
     <t>26/6</t>
   </si>
   <si>
-    <t>19/6</t>
-  </si>
-  <si>
     <t>24/6</t>
   </si>
   <si>
@@ -366,6 +363,9 @@
   </si>
   <si>
     <t>15/7</t>
+  </si>
+  <si>
+    <t>10/7</t>
   </si>
 </sst>
 </file>
@@ -440,11 +440,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -463,8 +464,10 @@
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -764,10 +767,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>104</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
@@ -787,7 +790,7 @@
         <v>64</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>14</v>
@@ -810,7 +813,7 @@
         <v>64</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>14</v>
@@ -833,7 +836,7 @@
         <v>64</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>14</v>
@@ -856,7 +859,7 @@
         <v>64</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>14</v>
@@ -879,7 +882,7 @@
         <v>64</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>14</v>
@@ -902,7 +905,7 @@
         <v>64</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>14</v>
@@ -924,8 +927,8 @@
       <c r="B8" t="s">
         <v>47</v>
       </c>
-      <c r="C8" t="s">
-        <v>101</v>
+      <c r="C8" s="9" t="s">
+        <v>106</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>14</v>
@@ -947,8 +950,8 @@
       <c r="B9" t="s">
         <v>60</v>
       </c>
-      <c r="C9" t="s">
-        <v>101</v>
+      <c r="C9" s="9" t="s">
+        <v>106</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>14</v>
@@ -956,7 +959,7 @@
       <c r="E9" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="10" t="s">
         <v>62</v>
       </c>
       <c r="G9" t="s">
@@ -970,8 +973,8 @@
       <c r="B10" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C10" t="s">
-        <v>101</v>
+      <c r="C10" s="9" t="s">
+        <v>106</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>14</v>
@@ -993,8 +996,8 @@
       <c r="B11" t="s">
         <v>47</v>
       </c>
-      <c r="C11" t="s">
-        <v>101</v>
+      <c r="C11" s="9" t="s">
+        <v>106</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>14</v>
@@ -1016,8 +1019,8 @@
       <c r="B12" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C12" t="s">
-        <v>101</v>
+      <c r="C12" s="9" t="s">
+        <v>106</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" t="s">
@@ -1038,7 +1041,7 @@
         <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D13" t="s">
         <v>14</v>
@@ -1061,7 +1064,7 @@
         <v>64</v>
       </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
         <v>14</v>
@@ -1084,7 +1087,7 @@
         <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>14</v>
@@ -1107,7 +1110,7 @@
         <v>64</v>
       </c>
       <c r="C16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>14</v>
@@ -1130,7 +1133,7 @@
         <v>64</v>
       </c>
       <c r="C17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D17" t="s">
         <v>14</v>
@@ -1153,7 +1156,7 @@
         <v>64</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>14</v>
@@ -1291,7 +1294,7 @@
         <v>11</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>14</v>
@@ -1314,7 +1317,7 @@
         <v>11</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>14</v>
@@ -1337,7 +1340,7 @@
         <v>6</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>14</v>
@@ -1360,7 +1363,7 @@
         <v>23</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>14</v>
@@ -1383,7 +1386,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="5" t="s">
@@ -1404,7 +1407,7 @@
         <v>19</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>14</v>

--- a/presentaciones.xlsx
+++ b/presentaciones.xlsx
@@ -1,24 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juanc\OneDrive\Documentos\LAB-MAA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e2f577dda2fcbe77/Documentos/LAB-MAA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5599A49-8769-41FA-9A77-460C77A4C51B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92B3A7D9-A9C9-4183-84C8-8767C1D8C6E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57330" yWindow="-270" windowWidth="21030" windowHeight="11340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1415" yWindow="1415" windowWidth="14400" windowHeight="7290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="AT2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$1</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="155">
   <si>
     <t>Estudiante</t>
   </si>
@@ -366,13 +368,157 @@
   </si>
   <si>
     <t>10/7</t>
+  </si>
+  <si>
+    <t>fmaluenda2025@udec.cl</t>
+  </si>
+  <si>
+    <t>Ingenieria civil biomedica</t>
+  </si>
+  <si>
+    <t>TRUE</t>
+  </si>
+  <si>
+    <t>isrivera2022@udec.cl</t>
+  </si>
+  <si>
+    <t>ICI</t>
+  </si>
+  <si>
+    <t>Jacevedo2020@udec.cl</t>
+  </si>
+  <si>
+    <t>ingenieria civil industrial</t>
+  </si>
+  <si>
+    <t>jmontesinos2021@udec.cl</t>
+  </si>
+  <si>
+    <t>ing civil industrial</t>
+  </si>
+  <si>
+    <t>josepriquelmem@gmail.com</t>
+  </si>
+  <si>
+    <t>psicología</t>
+  </si>
+  <si>
+    <t>marcelaparada@udec.cl</t>
+  </si>
+  <si>
+    <t>DII (académica)</t>
+  </si>
+  <si>
+    <t>Ngarrido2019@udec.cl</t>
+  </si>
+  <si>
+    <t>Ingeniería civil industrial</t>
+  </si>
+  <si>
+    <t>pvillavicen2021@udec.cl</t>
+  </si>
+  <si>
+    <t>Ing civil biomedica</t>
+  </si>
+  <si>
+    <t>FALSE</t>
+  </si>
+  <si>
+    <t>econstanzof2021@udec.cl</t>
+  </si>
+  <si>
+    <t>Industrial</t>
+  </si>
+  <si>
+    <t>esteban.g.santana@gmail.com</t>
+  </si>
+  <si>
+    <t>Psicología</t>
+  </si>
+  <si>
+    <t>mlozano2024@udec.cl</t>
+  </si>
+  <si>
+    <t>Ingeniería Civil Industrial</t>
+  </si>
+  <si>
+    <t>domedelpalaciosj@gmail.com</t>
+  </si>
+  <si>
+    <t>ING civil industrial</t>
+  </si>
+  <si>
+    <t>joarevalo2021@udec.cl</t>
+  </si>
+  <si>
+    <t>Sebastsoto2021@udec.cl</t>
+  </si>
+  <si>
+    <t>vicsaavedra2021@udec.cl</t>
+  </si>
+  <si>
+    <t>Ingenieria Civil Industrial</t>
+  </si>
+  <si>
+    <t>alosoto2021@udec.cl</t>
+  </si>
+  <si>
+    <t>martinvalenzuel@udec.cl</t>
+  </si>
+  <si>
+    <t>Oberrios@udec.com</t>
+  </si>
+  <si>
+    <t>Ciencias fisicas</t>
+  </si>
+  <si>
+    <t>jdomedel2024@udec.cl</t>
+  </si>
+  <si>
+    <t>Ingenieria civil industrial</t>
+  </si>
+  <si>
+    <t>jerices2022@udec.cl</t>
+  </si>
+  <si>
+    <t>raymunoz2022@udec.cl</t>
+  </si>
+  <si>
+    <t>franmeza2021@udec.cl</t>
+  </si>
+  <si>
+    <t>frrosas2021@udec.cl</t>
+  </si>
+  <si>
+    <t>Ingeniería industrial</t>
+  </si>
+  <si>
+    <t>dicarmine2021@udec.cl</t>
+  </si>
+  <si>
+    <t>Brneira2021@udec.cl</t>
+  </si>
+  <si>
+    <t>alwilson2021@udec.cl</t>
+  </si>
+  <si>
+    <t>viceortiz2021@udec.cl</t>
+  </si>
+  <si>
+    <t>Correo</t>
+  </si>
+  <si>
+    <t>Carrera</t>
+  </si>
+  <si>
+    <t>Asiste</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -416,8 +562,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF434343"/>
+      <name val="Roboto"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -436,6 +587,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F9FA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -451,7 +608,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -480,6 +637,18 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -1401,7 +1570,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="5" t="s">
@@ -1476,4 +1645,327 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A08FEF44-24AD-468F-97FA-66AB7EC58A69}">
+  <dimension ref="A1:C28"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <cols>
+    <col min="1" max="1" width="30.04296875" customWidth="1"/>
+    <col min="2" max="2" width="21.31640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="26.5" x14ac:dyDescent="0.75">
+      <c r="A2" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A3" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A4" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A5" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A6" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A7" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A8" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="26.5" x14ac:dyDescent="0.75">
+      <c r="A9" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="26.5" x14ac:dyDescent="0.75">
+      <c r="A10" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="26.5" x14ac:dyDescent="0.75">
+      <c r="A11" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A12" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A13" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A14" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A15" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="26.5" x14ac:dyDescent="0.75">
+      <c r="A16" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="26.5" x14ac:dyDescent="0.75">
+      <c r="A17" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A18" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A19" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A20" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="26.5" x14ac:dyDescent="0.75">
+      <c r="A21" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="26.5" x14ac:dyDescent="0.75">
+      <c r="A22" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A23" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="26.5" x14ac:dyDescent="0.75">
+      <c r="A24" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A25" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="C25" s="19" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A26" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A27" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A28" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>